--- a/artfynd/A 19275-2025 artfynd.xlsx
+++ b/artfynd/A 19275-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124326633</v>
+        <v>124326632</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>860462</v>
+        <v>860459</v>
       </c>
       <c r="R3" t="n">
-        <v>7374679</v>
+        <v>7374674</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124326632</v>
+        <v>124326633</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>860459</v>
+        <v>860462</v>
       </c>
       <c r="R4" t="n">
-        <v>7374674</v>
+        <v>7374679</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 19275-2025 artfynd.xlsx
+++ b/artfynd/A 19275-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124326632</v>
+        <v>124326633</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>860459</v>
+        <v>860462</v>
       </c>
       <c r="R3" t="n">
-        <v>7374674</v>
+        <v>7374679</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124326633</v>
+        <v>124326632</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>860462</v>
+        <v>860459</v>
       </c>
       <c r="R4" t="n">
-        <v>7374679</v>
+        <v>7374674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 19275-2025 artfynd.xlsx
+++ b/artfynd/A 19275-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820483</v>
+        <v>124326632</v>
       </c>
       <c r="B2" t="n">
-        <v>96891</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>860666</v>
+        <v>860459</v>
       </c>
       <c r="R2" t="n">
-        <v>7374635</v>
+        <v>7374674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +784,7 @@
         <v>124326633</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124326632</v>
+        <v>119820483</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>860459</v>
+        <v>860666</v>
       </c>
       <c r="R4" t="n">
-        <v>7374674</v>
+        <v>7374635</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,17 +956,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,6 +990,218 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124825370</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Boheden, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>860778</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7374614</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7119145</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92183</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>65</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Boheden, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>860702</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7374821</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-10-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-10-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesbedömning -Inventerare: Leif Nybom  ID;36911</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19275-2025 artfynd.xlsx
+++ b/artfynd/A 19275-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7119145</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124326632</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124326633</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820483</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825370</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>